--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1149,7 +1149,483 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-09-08 10:19:14</t>
+          <t>2026-09-03 09:45:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-09-03 10:47:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-09-04 13:34:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-09-08 14:55:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-09-08 16:06:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:51:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-09-22 11:43:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-09-22 16:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-09-24 14:33:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-09-24 15:16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-09-28 13:50:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:43:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:08:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-09-28 16:20:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-09-29 09:54:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-09-30 12:14:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:19:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:51:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:48:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-10-02 12:05:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-10-02 12:12:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:47:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-10-06 12:14:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:17:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:19:44</t>
         </is>
       </c>
     </row>
@@ -1414,13 +1890,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B1C88C0-1EE6-4073-BB50-1BBAC330E88A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{833D3D1A-593E-4811-8C7E-5EC7A9B88BC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C383DBE4-67B3-4949-9D9F-4D7417DE7E58}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6EBE6BA-EEEC-47BA-9A56-1C11CB6CB16A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B596CBFF-028B-42F4-90D1-C060990CCA13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6F87D1A-9030-4900-A804-4849AFF58E44}"/>
 </file>
--- a/log_acoes.xlsx
+++ b/log_acoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1626,6 +1626,108 @@
       <c r="C75" t="inlineStr">
         <is>
           <t>2026-10-06 15:19:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-10-06 16:49:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-10-06 17:01:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-10-07 10:48:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:25:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Atualizou os dados</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:17:54</t>
         </is>
       </c>
     </row>
@@ -1890,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{833D3D1A-593E-4811-8C7E-5EC7A9B88BC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2DD62FA-FE28-4640-A172-96E4790DD3D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6EBE6BA-EEEC-47BA-9A56-1C11CB6CB16A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A00815FD-82E4-4B2C-845C-BCC8A877EB8A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6F87D1A-9030-4900-A804-4849AFF58E44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{366BA7A1-62A6-4BBE-B44D-ED0B829D71AF}"/>
 </file>